--- a/books.xlsx
+++ b/books.xlsx
@@ -519,43 +519,73 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BK002</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cryptography and network security</t>
+          <t>df</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>William Stallings</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
+          <t>rh</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>hg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>yr</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bkoo4</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">yh </t>
+          <t>Computer Graphics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ghtdtr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Er. Rajiv Chopra</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S.Chand, New Delhi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
